--- a/Data/Rules/Tuesdays Natural Dog Rules Matrix.xlsx
+++ b/Data/Rules/Tuesdays Natural Dog Rules Matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="72">
   <si>
     <t>SKU</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>HQ_Max</t>
+  </si>
+  <si>
+    <t>Total Max</t>
   </si>
   <si>
     <t>26199</t>
@@ -558,10 +561,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN16"/>
+  <dimension ref="A1:AO16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:41">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -682,16 +685,19 @@
       <c r="AN1" t="s">
         <v>39</v>
       </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:41">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -804,16 +810,19 @@
       <c r="AN2">
         <v>0</v>
       </c>
+      <c r="AO2">
+        <v>40</v>
+      </c>
     </row>
-    <row r="3" spans="1:40">
+    <row r="3" spans="1:41">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -926,16 +935,19 @@
       <c r="AN3">
         <v>0</v>
       </c>
+      <c r="AO3">
+        <v>36</v>
+      </c>
     </row>
-    <row r="4" spans="1:40">
+    <row r="4" spans="1:41">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1016,10 +1028,10 @@
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF4" t="b">
         <v>0</v>
@@ -1048,16 +1060,19 @@
       <c r="AN4">
         <v>0</v>
       </c>
+      <c r="AO4">
+        <v>37</v>
+      </c>
     </row>
-    <row r="5" spans="1:40">
+    <row r="5" spans="1:41">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1170,16 +1185,19 @@
       <c r="AN5">
         <v>0</v>
       </c>
+      <c r="AO5">
+        <v>34</v>
+      </c>
     </row>
-    <row r="6" spans="1:40">
+    <row r="6" spans="1:41">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1292,16 +1310,19 @@
       <c r="AN6">
         <v>0</v>
       </c>
+      <c r="AO6">
+        <v>35</v>
+      </c>
     </row>
-    <row r="7" spans="1:40">
+    <row r="7" spans="1:41">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1414,16 +1435,19 @@
       <c r="AN7">
         <v>0</v>
       </c>
+      <c r="AO7">
+        <v>34</v>
+      </c>
     </row>
-    <row r="8" spans="1:40">
+    <row r="8" spans="1:41">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1536,16 +1560,19 @@
       <c r="AN8">
         <v>0</v>
       </c>
+      <c r="AO8">
+        <v>35</v>
+      </c>
     </row>
-    <row r="9" spans="1:40">
+    <row r="9" spans="1:41">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1658,16 +1685,19 @@
       <c r="AN9">
         <v>0</v>
       </c>
+      <c r="AO9">
+        <v>33</v>
+      </c>
     </row>
-    <row r="10" spans="1:40">
+    <row r="10" spans="1:41">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1780,16 +1810,19 @@
       <c r="AN10">
         <v>0</v>
       </c>
+      <c r="AO10">
+        <v>36</v>
+      </c>
     </row>
-    <row r="11" spans="1:40">
+    <row r="11" spans="1:41">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1902,16 +1935,19 @@
       <c r="AN11">
         <v>0</v>
       </c>
+      <c r="AO11">
+        <v>33</v>
+      </c>
     </row>
-    <row r="12" spans="1:40">
+    <row r="12" spans="1:41">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2024,382 +2060,394 @@
       <c r="AN12">
         <v>0</v>
       </c>
+      <c r="AO12">
+        <v>34</v>
+      </c>
     </row>
-    <row r="13" spans="1:40">
+    <row r="13" spans="1:41">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <v>3</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13">
+        <v>3</v>
+      </c>
+      <c r="N13" t="b">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>2</v>
+      </c>
+      <c r="P13">
+        <v>3</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>2</v>
+      </c>
+      <c r="S13">
+        <v>3</v>
+      </c>
+      <c r="T13" t="b">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>2</v>
+      </c>
+      <c r="V13">
+        <v>3</v>
+      </c>
+      <c r="W13" t="b">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>2</v>
+      </c>
+      <c r="Y13">
+        <v>3</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>2</v>
+      </c>
+      <c r="AB13">
+        <v>3</v>
+      </c>
+      <c r="AC13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>2</v>
+      </c>
+      <c r="AE13">
+        <v>3</v>
+      </c>
+      <c r="AF13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>2</v>
+      </c>
+      <c r="AH13">
+        <v>3</v>
+      </c>
+      <c r="AI13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>2</v>
+      </c>
+      <c r="AK13">
+        <v>3</v>
+      </c>
+      <c r="AL13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:41">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14">
+        <v>3</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>2</v>
+      </c>
+      <c r="M14">
+        <v>3</v>
+      </c>
+      <c r="N14" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>2</v>
+      </c>
+      <c r="P14">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>2</v>
+      </c>
+      <c r="S14">
+        <v>3</v>
+      </c>
+      <c r="T14" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>2</v>
+      </c>
+      <c r="V14">
+        <v>3</v>
+      </c>
+      <c r="W14" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>2</v>
+      </c>
+      <c r="Y14">
+        <v>3</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>2</v>
+      </c>
+      <c r="AB14">
+        <v>3</v>
+      </c>
+      <c r="AC14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>2</v>
+      </c>
+      <c r="AE14">
+        <v>3</v>
+      </c>
+      <c r="AF14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>2</v>
+      </c>
+      <c r="AH14">
+        <v>3</v>
+      </c>
+      <c r="AI14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>2</v>
+      </c>
+      <c r="AK14">
+        <v>3</v>
+      </c>
+      <c r="AL14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:41">
+      <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15">
+        <v>3</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>2</v>
+      </c>
+      <c r="M15">
+        <v>3</v>
+      </c>
+      <c r="N15" t="b">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>2</v>
+      </c>
+      <c r="P15">
+        <v>3</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>2</v>
+      </c>
+      <c r="S15">
+        <v>3</v>
+      </c>
+      <c r="T15" t="b">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>2</v>
+      </c>
+      <c r="V15">
+        <v>3</v>
+      </c>
+      <c r="W15" t="b">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>2</v>
+      </c>
+      <c r="Y15">
+        <v>3</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>2</v>
+      </c>
+      <c r="AB15">
+        <v>3</v>
+      </c>
+      <c r="AC15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>2</v>
+      </c>
+      <c r="AE15">
+        <v>3</v>
+      </c>
+      <c r="AF15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>2</v>
+      </c>
+      <c r="AH15">
+        <v>3</v>
+      </c>
+      <c r="AI15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>2</v>
+      </c>
+      <c r="AK15">
+        <v>3</v>
+      </c>
+      <c r="AL15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:41">
+      <c r="A16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" t="s">
         <v>70</v>
       </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>2</v>
-      </c>
-      <c r="G13">
-        <v>3</v>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>2</v>
-      </c>
-      <c r="J13">
-        <v>3</v>
-      </c>
-      <c r="K13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>2</v>
-      </c>
-      <c r="M13">
-        <v>3</v>
-      </c>
-      <c r="N13" t="b">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>2</v>
-      </c>
-      <c r="P13">
-        <v>3</v>
-      </c>
-      <c r="Q13" t="b">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>2</v>
-      </c>
-      <c r="S13">
-        <v>3</v>
-      </c>
-      <c r="T13" t="b">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>2</v>
-      </c>
-      <c r="V13">
-        <v>3</v>
-      </c>
-      <c r="W13" t="b">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>2</v>
-      </c>
-      <c r="Y13">
-        <v>3</v>
-      </c>
-      <c r="Z13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>2</v>
-      </c>
-      <c r="AB13">
-        <v>3</v>
-      </c>
-      <c r="AC13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <v>2</v>
-      </c>
-      <c r="AE13">
-        <v>3</v>
-      </c>
-      <c r="AF13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>2</v>
-      </c>
-      <c r="AH13">
-        <v>3</v>
-      </c>
-      <c r="AI13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ13">
-        <v>2</v>
-      </c>
-      <c r="AK13">
-        <v>3</v>
-      </c>
-      <c r="AL13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:40">
-      <c r="A14" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>2</v>
-      </c>
-      <c r="G14">
-        <v>3</v>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>2</v>
-      </c>
-      <c r="J14">
-        <v>3</v>
-      </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>2</v>
-      </c>
-      <c r="M14">
-        <v>3</v>
-      </c>
-      <c r="N14" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>2</v>
-      </c>
-      <c r="P14">
-        <v>3</v>
-      </c>
-      <c r="Q14" t="b">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>2</v>
-      </c>
-      <c r="S14">
-        <v>3</v>
-      </c>
-      <c r="T14" t="b">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>2</v>
-      </c>
-      <c r="V14">
-        <v>3</v>
-      </c>
-      <c r="W14" t="b">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>2</v>
-      </c>
-      <c r="Y14">
-        <v>3</v>
-      </c>
-      <c r="Z14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>2</v>
-      </c>
-      <c r="AB14">
-        <v>3</v>
-      </c>
-      <c r="AC14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD14">
-        <v>2</v>
-      </c>
-      <c r="AE14">
-        <v>3</v>
-      </c>
-      <c r="AF14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14">
-        <v>2</v>
-      </c>
-      <c r="AH14">
-        <v>3</v>
-      </c>
-      <c r="AI14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ14">
-        <v>2</v>
-      </c>
-      <c r="AK14">
-        <v>3</v>
-      </c>
-      <c r="AL14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:40">
-      <c r="A15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>2</v>
-      </c>
-      <c r="G15">
-        <v>3</v>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>2</v>
-      </c>
-      <c r="J15">
-        <v>3</v>
-      </c>
-      <c r="K15" t="b">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>2</v>
-      </c>
-      <c r="M15">
-        <v>3</v>
-      </c>
-      <c r="N15" t="b">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>2</v>
-      </c>
-      <c r="P15">
-        <v>3</v>
-      </c>
-      <c r="Q15" t="b">
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>2</v>
-      </c>
-      <c r="S15">
-        <v>3</v>
-      </c>
-      <c r="T15" t="b">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>2</v>
-      </c>
-      <c r="V15">
-        <v>3</v>
-      </c>
-      <c r="W15" t="b">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>2</v>
-      </c>
-      <c r="Y15">
-        <v>3</v>
-      </c>
-      <c r="Z15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <v>2</v>
-      </c>
-      <c r="AB15">
-        <v>3</v>
-      </c>
-      <c r="AC15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <v>2</v>
-      </c>
-      <c r="AE15">
-        <v>3</v>
-      </c>
-      <c r="AF15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15">
-        <v>2</v>
-      </c>
-      <c r="AH15">
-        <v>3</v>
-      </c>
-      <c r="AI15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ15">
-        <v>2</v>
-      </c>
-      <c r="AK15">
-        <v>3</v>
-      </c>
-      <c r="AL15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-      <c r="AN15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:40">
-      <c r="A16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" t="s">
-        <v>69</v>
-      </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -2511,6 +2559,9 @@
       </c>
       <c r="AN16">
         <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Rules/Tuesdays Natural Dog Rules Matrix.xlsx
+++ b/Data/Rules/Tuesdays Natural Dog Rules Matrix.xlsx
@@ -840,10 +840,10 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
@@ -876,10 +876,10 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W3" t="b">
         <v>0</v>
@@ -912,10 +912,10 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI3" t="b">
         <v>0</v>
@@ -936,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:41">
